--- a/artfynd/A 2893-2023 artfynd.xlsx
+++ b/artfynd/A 2893-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2893-2023 artfynd.xlsx
+++ b/artfynd/A 2893-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111098234</v>
+        <v>111096965</v>
       </c>
       <c r="B2" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,35 +686,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svarvarmyran (Svarvarmyran), Ly lm</t>
+          <t>Svarvarmyran, Svarvarmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691073.2524526344</v>
+        <v>690885</v>
       </c>
       <c r="R2" t="n">
-        <v>7125392.573882032</v>
+        <v>7125535</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,7 +746,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +756,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,15 +783,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111098394</v>
+        <v>111098261</v>
       </c>
       <c r="B3" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,35 +794,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svarvarmyran (Svarvarmyran), Ly lm</t>
+          <t>Svarvarmyran, Svarvarmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691134.098742541</v>
+        <v>691089</v>
       </c>
       <c r="R3" t="n">
-        <v>7125490.231860189</v>
+        <v>7125441</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,7 +854,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +864,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,16 +894,11 @@
         <v>111098845</v>
       </c>
       <c r="B4" t="n">
-        <v>90666</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -938,14 +923,14 @@
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svarvarmyran (Svarvarmyran), Ly lm</t>
+          <t>Svarvarmyran, Svarvarmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>690976.0699309894</v>
+        <v>690976</v>
       </c>
       <c r="R4" t="n">
-        <v>7125479.131126685</v>
+        <v>7125480</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,19 +999,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111098261</v>
+        <v>112124849</v>
       </c>
       <c r="B5" t="n">
-        <v>90666</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1051,17 +1031,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svarvarmyran (Svarvarmyran), Ly lm</t>
+          <t>Svarvarmyran, Svarvarmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691088.6354497015</v>
+        <v>690915</v>
       </c>
       <c r="R5" t="n">
-        <v>7125440.689382236</v>
+        <v>7125491</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,22 +1065,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-07-27</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-07-27</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,6 +1104,330 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>112125005</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Svarvarmyran, Svarvarmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>690916</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7125490</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-09-16</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-09-16</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>111098234</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Svarvarmyran, Svarvarmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>691074</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7125392</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>111098394</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Svarvarmyran, Svarvarmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>691134</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7125490</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2893-2023 artfynd.xlsx
+++ b/artfynd/A 2893-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111096965</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111098261</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111098845</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112124849</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112125005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1320,6 +1350,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111098234</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1428,8 +1463,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111098394</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>